--- a/artfynd/A 26944-2024 artfynd.xlsx
+++ b/artfynd/A 26944-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80512567</v>
+        <v>80512577</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435745.9448539581</v>
+        <v>435509</v>
       </c>
       <c r="R2" t="n">
-        <v>6964258.222548615</v>
+        <v>6964383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80512577</v>
+        <v>80512567</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435509.2205985077</v>
+        <v>435746</v>
       </c>
       <c r="R3" t="n">
-        <v>6964383.196473971</v>
+        <v>6964258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26944-2024 artfynd.xlsx
+++ b/artfynd/A 26944-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80512577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80512567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>